--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -187,12 +187,12 @@
     <t>Dynamo Kyiv</t>
   </si>
   <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
@@ -217,10 +217,10 @@
     <t>Hamrun Spartans</t>
   </si>
   <si>
+    <t>Slovan Bratislava</t>
+  </si>
+  <si>
     <t>Lincoln Red Imps</t>
-  </si>
-  <si>
-    <t>Slovan Bratislava</t>
   </si>
   <si>
     <t>Miami FC II</t>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -160,12 +160,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -181,27 +181,27 @@
     <t>Kairat</t>
   </si>
   <si>
+    <t>Dynamo Kyiv</t>
+  </si>
+  <si>
     <t>Drita</t>
   </si>
   <si>
-    <t>Dynamo Kyiv</t>
+    <t>Red Star Belgrade</t>
   </si>
   <si>
     <t>Zrinjski</t>
   </si>
   <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Criciúma</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
@@ -211,25 +211,25 @@
     <t>KuPS</t>
   </si>
   <si>
+    <t>Hamrun Spartans</t>
+  </si>
+  <si>
     <t>København</t>
   </si>
   <si>
-    <t>Hamrun Spartans</t>
+    <t>Lincoln Red Imps</t>
   </si>
   <si>
     <t>Slovan Bratislava</t>
   </si>
   <si>
-    <t>Lincoln Red Imps</t>
-  </si>
-  <si>
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -1452,13 +1452,13 @@
         <v>73</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         <v>45867</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
@@ -1568,13 +1568,13 @@
         <v>73</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1616,10 +1616,10 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -1646,7 +1646,7 @@
         <v>74</v>
       </c>
       <c r="AL9" s="3">
-        <v>45867.83333333334</v>
+        <v>45867.85416666666</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1684,13 +1684,13 @@
         <v>73</v>
       </c>
       <c r="L10">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1732,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD10">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.06</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>28</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.06</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>28</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.06</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>28</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL11"/>
+  <dimension ref="A1:AL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.39</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1945,6 +1945,138 @@
       </c>
       <c r="AL11" s="3" t="n">
         <v>45867.875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL12" s="3" t="n">
+        <v>45867.89930555555</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -992,10 +992,10 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.06</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>28</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.06</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>28</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>13</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.39</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>13</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.06</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>28</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.39</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>13</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>3.81</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.57</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>3.81</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.39</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.06</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>28</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>3.81</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -815,43 +815,43 @@
         <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB3" t="n">
         <v>1.75</v>
@@ -860,22 +860,22 @@
         <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>3.81</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>13</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1118,16 +1118,16 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V4" t="n">
         <v>4.6</v>
       </c>
-      <c r="N4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.95</v>
+        <v>2.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,40 +1070,40 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1118,22 +1118,22 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1211,43 +1211,43 @@
         <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AB6" t="n">
         <v>1.8</v>
@@ -1256,22 +1256,22 @@
         <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1343,49 +1343,49 @@
         <v>28</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
         <v>1.67</v>
@@ -1394,16 +1394,16 @@
         <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>3.81</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1772,16 +1772,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O6" t="n">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="P6" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>7.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="V6" t="n">
-        <v>6.35</v>
+        <v>3.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.48</v>
+        <v>7.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>3.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.09</v>
+        <v>1.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.65</v>
+        <v>2.74</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.06</v>
       </c>
-      <c r="M7" t="n">
-        <v>11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>28</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P7" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.1</v>
+        <v>3.48</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.74</v>
+        <v>5.65</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1475,67 +1475,67 @@
         <v>5.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -1607,37 +1607,37 @@
         <v>3.81</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z9" t="n">
         <v>1.48</v>
@@ -1652,22 +1652,22 @@
         <v>1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1739,43 +1739,43 @@
         <v>3.03</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="n">
         <v>2.09</v>
@@ -1784,22 +1784,22 @@
         <v>1.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2003,43 +2003,43 @@
         <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB12" t="n">
         <v>2.2</v>
@@ -2048,22 +2048,22 @@
         <v>1.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>13</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V5" t="n">
         <v>4.6</v>
       </c>
-      <c r="N5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>2.53</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P9" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.15</v>
+        <v>3.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="n">
-        <v>10</v>
+        <v>6.65</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.15</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.75</v>
+        <v>5.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="n">
-        <v>6.65</v>
+        <v>10</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.06</v>
       </c>
-      <c r="M6" t="n">
-        <v>11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>28</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P6" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.1</v>
+        <v>3.48</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.74</v>
+        <v>5.65</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O7" t="n">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="P7" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96</v>
+        <v>7.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="S7" t="n">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="V7" t="n">
-        <v>6.35</v>
+        <v>3.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.48</v>
+        <v>7.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>3.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.09</v>
+        <v>1.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.65</v>
+        <v>2.74</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V4" t="n">
         <v>4.6</v>
       </c>
-      <c r="N4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V4" t="n">
-        <v>6</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.53</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         <v>7.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD7" t="n">
         <v>1.67</v>
@@ -1517,22 +1517,22 @@
         <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
         <v>3.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
         <v>1.73</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.75</v>
+        <v>6.2</v>
       </c>
       <c r="AI8" t="n">
         <v>1.09</v>
@@ -1622,28 +1622,28 @@
         <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="Z9" t="n">
         <v>1.32</v>
       </c>
       <c r="AA9" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AB9" t="n">
         <v>2.09</v>
@@ -1652,10 +1652,10 @@
         <v>1.74</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF9" t="n">
         <v>1.8</v>
@@ -1664,10 +1664,10 @@
         <v>1.91</v>
       </c>
       <c r="AH9" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1754,22 +1754,22 @@
         <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="Z10" t="n">
         <v>1.48</v>
@@ -1784,10 +1784,10 @@
         <v>1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
         <v>2.19</v>
@@ -2012,34 +2012,34 @@
         <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
         <v>2.45</v>
       </c>
       <c r="T12" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
         <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
         <v>2.2</v>
@@ -2048,7 +2048,7 @@
         <v>1.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AE12" t="n">
         <v>1.2</v>
@@ -2060,10 +2060,10 @@
         <v>1.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O6" t="n">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="P6" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>7.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="V6" t="n">
-        <v>6.35</v>
+        <v>3.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.48</v>
+        <v>7.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.09</v>
+        <v>1.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.65</v>
+        <v>2.74</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.06</v>
       </c>
-      <c r="M7" t="n">
-        <v>11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>28</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P7" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.1</v>
+        <v>3.48</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.74</v>
+        <v>5.65</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.15</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P9" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="U9" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>6.95</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.08</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P10" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.02</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.04</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>13</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V5" t="n">
         <v>4.6</v>
       </c>
-      <c r="N5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M8" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.5</v>
@@ -1487,22 +1487,22 @@
         <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W8" t="n">
         <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
         <v>9</v>
@@ -1526,13 +1526,13 @@
         <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.2</v>
+        <v>6.75</v>
       </c>
       <c r="AI8" t="n">
         <v>1.09</v>
@@ -1601,10 +1601,10 @@
         <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>1.77</v>
@@ -1616,7 +1616,7 @@
         <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
         <v>2.15</v>
@@ -1625,13 +1625,13 @@
         <v>3.55</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
         <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1.06</v>
@@ -1640,31 +1640,31 @@
         <v>7.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.37</v>
+        <v>2.53</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI9" t="n">
         <v>1.04</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>5.22</v>
       </c>
       <c r="O12" t="n">
         <v>1.57</v>
@@ -2012,46 +2012,46 @@
         <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U12" t="n">
         <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.2</v>
+        <v>7.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AD12" t="n">
         <v>3.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
@@ -2060,10 +2060,10 @@
         <v>1.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V4" t="n">
         <v>4.6</v>
       </c>
-      <c r="N4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V4" t="n">
-        <v>6</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P9" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.04</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.15</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>11</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.25</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="AG10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.06</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
   <si>
     <t>Date</t>
   </si>
@@ -151,6 +151,9 @@
     <t>21:00</t>
   </si>
   <si>
+    <t>21:35</t>
+  </si>
+  <si>
     <t>Norway Toppserien</t>
   </si>
   <si>
@@ -160,12 +163,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -181,12 +184,12 @@
     <t>Kairat</t>
   </si>
   <si>
+    <t>Drita</t>
+  </si>
+  <si>
     <t>Dynamo Kyiv</t>
   </si>
   <si>
-    <t>Drita</t>
-  </si>
-  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
@@ -196,27 +199,30 @@
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
     <t>Grêmio</t>
   </si>
   <si>
-    <t>Criciúma</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
+    <t>Goiás</t>
+  </si>
+  <si>
     <t>Røa Women</t>
   </si>
   <si>
     <t>KuPS</t>
   </si>
   <si>
+    <t>København</t>
+  </si>
+  <si>
     <t>Hamrun Spartans</t>
   </si>
   <si>
-    <t>København</t>
-  </si>
-  <si>
     <t>Lincoln Red Imps</t>
   </si>
   <si>
@@ -226,16 +232,22 @@
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Cavalry FC</t>
   </si>
   <si>
+    <t>Remo</t>
+  </si>
+  <si>
     <t>incomplete</t>
+  </si>
+  <si>
+    <t>suspended</t>
   </si>
   <si>
     <t>[]</t>
@@ -602,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL11"/>
+  <dimension ref="A1:AL12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -729,16 +741,16 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -753,7 +765,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -828,10 +840,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL2" s="3">
         <v>45867.45833333334</v>
@@ -845,16 +857,16 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -869,85 +881,85 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL3" s="3">
         <v>45867.5</v>
@@ -961,16 +973,16 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -985,43 +997,43 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
         <v>0</v>
@@ -1036,10 +1048,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -1048,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -1060,10 +1072,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL4" s="3">
         <v>45867.625</v>
@@ -1077,16 +1089,16 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1101,85 +1113,85 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL5" s="3">
         <v>45867.625</v>
@@ -1193,109 +1205,109 @@
         <v>41</v>
       </c>
       <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6">
+        <v>1.06</v>
+      </c>
+      <c r="M6">
+        <v>11</v>
+      </c>
+      <c r="N6">
+        <v>28</v>
+      </c>
+      <c r="O6">
+        <v>1.07</v>
+      </c>
+      <c r="P6">
         <v>46</v>
       </c>
-      <c r="D6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>73</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
       <c r="Q6">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AJ6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL6" s="3">
         <v>45867.66666666666</v>
@@ -1309,16 +1321,16 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1333,85 +1345,85 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL7" s="3">
         <v>45867.66666666666</v>
@@ -1425,16 +1437,16 @@
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1449,85 +1461,85 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L8">
+        <v>1.53</v>
+      </c>
+      <c r="M8">
+        <v>3.6</v>
+      </c>
+      <c r="N8">
+        <v>5.5</v>
+      </c>
+      <c r="O8">
         <v>1.5</v>
       </c>
-      <c r="M8">
-        <v>3.85</v>
-      </c>
-      <c r="N8">
-        <v>5.8</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL8" s="3">
         <v>45867.83333333334</v>
@@ -1541,16 +1553,16 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1565,85 +1577,85 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L9">
+        <v>1.95</v>
+      </c>
+      <c r="M9">
+        <v>2.9</v>
+      </c>
+      <c r="N9">
+        <v>3.81</v>
+      </c>
+      <c r="O9">
+        <v>1.77</v>
+      </c>
+      <c r="P9">
+        <v>6.5</v>
+      </c>
+      <c r="Q9">
+        <v>2.65</v>
+      </c>
+      <c r="R9">
+        <v>1.6</v>
+      </c>
+      <c r="S9">
         <v>2.15</v>
       </c>
-      <c r="M9">
-        <v>3.08</v>
-      </c>
-      <c r="N9">
-        <v>3.03</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB9">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AC9">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL9" s="3">
         <v>45867.85416666666</v>
@@ -1657,16 +1669,16 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1681,85 +1693,85 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL10" s="3">
         <v>45867.85416666666</v>
@@ -1773,16 +1785,16 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1797,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1872,13 +1884,129 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AK11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AL11" s="3">
         <v>45867.875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38">
+      <c r="A12" s="2">
+        <v>45867</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12">
+        <v>1.48</v>
+      </c>
+      <c r="M12">
+        <v>3.57</v>
+      </c>
+      <c r="N12">
+        <v>6</v>
+      </c>
+      <c r="O12">
+        <v>1.57</v>
+      </c>
+      <c r="P12">
+        <v>7.5</v>
+      </c>
+      <c r="Q12">
+        <v>3.1</v>
+      </c>
+      <c r="R12">
+        <v>1.48</v>
+      </c>
+      <c r="S12">
+        <v>2.5</v>
+      </c>
+      <c r="T12">
+        <v>3.2</v>
+      </c>
+      <c r="U12">
+        <v>1.3</v>
+      </c>
+      <c r="V12">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W12">
+        <v>1.06</v>
+      </c>
+      <c r="X12">
+        <v>1.04</v>
+      </c>
+      <c r="Y12">
+        <v>9</v>
+      </c>
+      <c r="Z12">
+        <v>1.42</v>
+      </c>
+      <c r="AA12">
+        <v>2.62</v>
+      </c>
+      <c r="AB12">
+        <v>2.2</v>
+      </c>
+      <c r="AC12">
+        <v>1.55</v>
+      </c>
+      <c r="AD12">
+        <v>3.9</v>
+      </c>
+      <c r="AE12">
+        <v>1.2</v>
+      </c>
+      <c r="AF12">
+        <v>2</v>
+      </c>
+      <c r="AG12">
+        <v>1.67</v>
+      </c>
+      <c r="AH12">
+        <v>9.5</v>
+      </c>
+      <c r="AI12">
+        <v>1.02</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL12" s="3">
+        <v>45867.89930555555</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -163,12 +163,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -199,12 +199,12 @@
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Criciúma</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
@@ -232,10 +232,10 @@
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -1464,19 +1464,19 @@
         <v>76</v>
       </c>
       <c r="L8">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="N8">
-        <v>5.5</v>
+        <v>5.32</v>
       </c>
       <c r="O8">
         <v>1.5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -1485,22 +1485,22 @@
         <v>1.4</v>
       </c>
       <c r="S8">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="T8">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V8">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1527,7 +1527,7 @@
         <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH8">
         <v>6.75</v>
@@ -1580,76 +1580,76 @@
         <v>76</v>
       </c>
       <c r="L9">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M9">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N9">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O9">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P9">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R9">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="S9">
-        <v>2.15</v>
+        <v>2.54</v>
       </c>
       <c r="T9">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="U9">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V9">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
+        <v>1.05</v>
+      </c>
+      <c r="Y9">
+        <v>10</v>
+      </c>
+      <c r="Z9">
+        <v>1.36</v>
+      </c>
+      <c r="AA9">
+        <v>2.88</v>
+      </c>
+      <c r="AB9">
+        <v>2.09</v>
+      </c>
+      <c r="AC9">
+        <v>1.74</v>
+      </c>
+      <c r="AD9">
+        <v>3.8</v>
+      </c>
+      <c r="AE9">
+        <v>1.22</v>
+      </c>
+      <c r="AF9">
+        <v>1.88</v>
+      </c>
+      <c r="AG9">
+        <v>1.88</v>
+      </c>
+      <c r="AH9">
+        <v>7.2</v>
+      </c>
+      <c r="AI9">
         <v>1.06</v>
-      </c>
-      <c r="Y9">
-        <v>6</v>
-      </c>
-      <c r="Z9">
-        <v>1.48</v>
-      </c>
-      <c r="AA9">
-        <v>2.37</v>
-      </c>
-      <c r="AB9">
-        <v>2.45</v>
-      </c>
-      <c r="AC9">
-        <v>1.5</v>
-      </c>
-      <c r="AD9">
-        <v>5</v>
-      </c>
-      <c r="AE9">
-        <v>1.14</v>
-      </c>
-      <c r="AF9">
-        <v>2.1</v>
-      </c>
-      <c r="AG9">
-        <v>1.6</v>
-      </c>
-      <c r="AH9">
-        <v>13</v>
-      </c>
-      <c r="AI9">
-        <v>1.04</v>
       </c>
       <c r="AJ9" t="s">
         <v>78</v>
@@ -1696,76 +1696,76 @@
         <v>76</v>
       </c>
       <c r="L10">
+        <v>1.95</v>
+      </c>
+      <c r="M10">
+        <v>2.9</v>
+      </c>
+      <c r="N10">
+        <v>3.81</v>
+      </c>
+      <c r="O10">
+        <v>1.77</v>
+      </c>
+      <c r="P10">
+        <v>6.5</v>
+      </c>
+      <c r="Q10">
+        <v>2.65</v>
+      </c>
+      <c r="R10">
+        <v>1.57</v>
+      </c>
+      <c r="S10">
         <v>2.15</v>
       </c>
-      <c r="M10">
-        <v>3.08</v>
-      </c>
-      <c r="N10">
-        <v>3.03</v>
-      </c>
-      <c r="O10">
-        <v>1.85</v>
-      </c>
-      <c r="P10">
-        <v>8</v>
-      </c>
-      <c r="Q10">
-        <v>2.25</v>
-      </c>
-      <c r="R10">
-        <v>1.43</v>
-      </c>
-      <c r="S10">
-        <v>2.54</v>
-      </c>
       <c r="T10">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="V10">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z10">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AA10">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="AB10">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AC10">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AD10">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AH10">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AI10">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
         <v>78</v>
@@ -1901,7 +1901,7 @@
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
@@ -1946,19 +1946,19 @@
         <v>3.1</v>
       </c>
       <c r="R12">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S12">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
         <v>1.3</v>
       </c>
       <c r="V12">
-        <v>8.300000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="W12">
         <v>1.06</v>
@@ -1967,7 +1967,7 @@
         <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="Z12">
         <v>1.42</v>
@@ -1982,7 +1982,7 @@
         <v>1.55</v>
       </c>
       <c r="AD12">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AE12">
         <v>1.2</v>
@@ -1997,7 +1997,7 @@
         <v>9.5</v>
       </c>
       <c r="AI12">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
         <v>78</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="78">
   <si>
     <t>Date</t>
   </si>
@@ -163,12 +163,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -190,21 +190,21 @@
     <t>Dynamo Kyiv</t>
   </si>
   <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
     <t>Grêmio</t>
   </si>
   <si>
-    <t>Criciúma</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
@@ -223,21 +223,21 @@
     <t>Hamrun Spartans</t>
   </si>
   <si>
+    <t>Slovan Bratislava</t>
+  </si>
+  <si>
     <t>Lincoln Red Imps</t>
   </si>
   <si>
-    <t>Slovan Bratislava</t>
-  </si>
-  <si>
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
   </si>
   <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
     <t>Cavalry FC</t>
   </si>
   <si>
@@ -245,9 +245,6 @@
   </si>
   <si>
     <t>incomplete</t>
-  </si>
-  <si>
-    <t>suspended</t>
   </si>
   <si>
     <t>[]</t>
@@ -840,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL2" s="3">
         <v>45867.45833333334</v>
@@ -956,10 +953,10 @@
         <v>1.08</v>
       </c>
       <c r="AJ3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL3" s="3">
         <v>45867.5</v>
@@ -1072,10 +1069,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL4" s="3">
         <v>45867.625</v>
@@ -1188,10 +1185,10 @@
         <v>1.23</v>
       </c>
       <c r="AJ5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL5" s="3">
         <v>45867.625</v>
@@ -1232,82 +1229,82 @@
         <v>76</v>
       </c>
       <c r="L6">
+        <v>2.75</v>
+      </c>
+      <c r="M6">
+        <v>3.4</v>
+      </c>
+      <c r="N6">
+        <v>2.42</v>
+      </c>
+      <c r="O6">
+        <v>2.02</v>
+      </c>
+      <c r="P6">
+        <v>11.5</v>
+      </c>
+      <c r="Q6">
+        <v>1.96</v>
+      </c>
+      <c r="R6">
+        <v>1.35</v>
+      </c>
+      <c r="S6">
+        <v>2.84</v>
+      </c>
+      <c r="T6">
+        <v>2.6</v>
+      </c>
+      <c r="U6">
+        <v>1.41</v>
+      </c>
+      <c r="V6">
+        <v>6.35</v>
+      </c>
+      <c r="W6">
         <v>1.06</v>
       </c>
-      <c r="M6">
-        <v>11</v>
-      </c>
-      <c r="N6">
-        <v>28</v>
-      </c>
-      <c r="O6">
-        <v>1.07</v>
-      </c>
-      <c r="P6">
-        <v>46</v>
-      </c>
-      <c r="Q6">
-        <v>7.3</v>
-      </c>
-      <c r="R6">
-        <v>1.1</v>
-      </c>
-      <c r="S6">
-        <v>5.1</v>
-      </c>
-      <c r="T6">
-        <v>1.82</v>
-      </c>
-      <c r="U6">
-        <v>1.88</v>
-      </c>
-      <c r="V6">
-        <v>3.5</v>
-      </c>
-      <c r="W6">
-        <v>1.22</v>
-      </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z6">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AA6">
-        <v>7.1</v>
+        <v>3.48</v>
       </c>
       <c r="AB6">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD6">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="AE6">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF6">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG6">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AH6">
-        <v>2.74</v>
+        <v>5.65</v>
       </c>
       <c r="AI6">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL6" s="3">
         <v>45867.66666666666</v>
@@ -1348,82 +1345,82 @@
         <v>76</v>
       </c>
       <c r="L7">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M7">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N7">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O7">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="P7">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="Q7">
-        <v>1.96</v>
+        <v>7.3</v>
       </c>
       <c r="R7">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="S7">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="T7">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="U7">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="V7">
-        <v>6.35</v>
+        <v>3.5</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AA7">
-        <v>3.48</v>
+        <v>7.1</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AC7">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="AD7">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE7">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF7">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="AG7">
-        <v>2.09</v>
+        <v>1.42</v>
       </c>
       <c r="AH7">
-        <v>5.65</v>
+        <v>2.74</v>
       </c>
       <c r="AI7">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AJ7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL7" s="3">
         <v>45867.66666666666</v>
@@ -1536,10 +1533,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL8" s="3">
         <v>45867.83333333334</v>
@@ -1580,82 +1577,82 @@
         <v>76</v>
       </c>
       <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>3.06</v>
+      </c>
+      <c r="N9">
+        <v>4</v>
+      </c>
+      <c r="O9">
+        <v>1.77</v>
+      </c>
+      <c r="P9">
+        <v>6.5</v>
+      </c>
+      <c r="Q9">
+        <v>2.65</v>
+      </c>
+      <c r="R9">
+        <v>1.56</v>
+      </c>
+      <c r="S9">
         <v>2.15</v>
       </c>
-      <c r="M9">
-        <v>3.08</v>
-      </c>
-      <c r="N9">
-        <v>3.03</v>
-      </c>
-      <c r="O9">
-        <v>1.85</v>
-      </c>
-      <c r="P9">
-        <v>8</v>
-      </c>
-      <c r="Q9">
+      <c r="T9">
+        <v>3.55</v>
+      </c>
+      <c r="U9">
+        <v>1.25</v>
+      </c>
+      <c r="V9">
+        <v>11</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>1.09</v>
+      </c>
+      <c r="Y9">
+        <v>6</v>
+      </c>
+      <c r="Z9">
+        <v>1.52</v>
+      </c>
+      <c r="AA9">
+        <v>2.47</v>
+      </c>
+      <c r="AB9">
+        <v>2.6</v>
+      </c>
+      <c r="AC9">
+        <v>1.44</v>
+      </c>
+      <c r="AD9">
+        <v>5</v>
+      </c>
+      <c r="AE9">
+        <v>1.11</v>
+      </c>
+      <c r="AF9">
         <v>2.25</v>
       </c>
-      <c r="R9">
-        <v>1.43</v>
-      </c>
-      <c r="S9">
-        <v>2.54</v>
-      </c>
-      <c r="T9">
-        <v>3.29</v>
-      </c>
-      <c r="U9">
-        <v>1.32</v>
-      </c>
-      <c r="V9">
-        <v>7.4</v>
-      </c>
-      <c r="W9">
-        <v>1.03</v>
-      </c>
-      <c r="X9">
-        <v>1.05</v>
-      </c>
-      <c r="Y9">
+      <c r="AG9">
+        <v>1.64</v>
+      </c>
+      <c r="AH9">
         <v>10</v>
       </c>
-      <c r="Z9">
-        <v>1.36</v>
-      </c>
-      <c r="AA9">
-        <v>2.88</v>
-      </c>
-      <c r="AB9">
-        <v>2.09</v>
-      </c>
-      <c r="AC9">
-        <v>1.74</v>
-      </c>
-      <c r="AD9">
-        <v>3.8</v>
-      </c>
-      <c r="AE9">
-        <v>1.22</v>
-      </c>
-      <c r="AF9">
-        <v>1.88</v>
-      </c>
-      <c r="AG9">
-        <v>1.88</v>
-      </c>
-      <c r="AH9">
-        <v>7.2</v>
-      </c>
       <c r="AI9">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL9" s="3">
         <v>45867.85416666666</v>
@@ -1696,82 +1693,82 @@
         <v>76</v>
       </c>
       <c r="L10">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M10">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N10">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O10">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P10">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="S10">
-        <v>2.15</v>
+        <v>2.54</v>
       </c>
       <c r="T10">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="U10">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V10">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AA10">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="AB10">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AC10">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD10">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AE10">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AG10">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AH10">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AI10">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL10" s="3">
         <v>45867.85416666666</v>
@@ -1884,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL11" s="3">
         <v>45867.875</v>
@@ -1901,7 +1898,7 @@
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
@@ -1925,16 +1922,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L12">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="M12">
-        <v>3.57</v>
+        <v>3.42</v>
       </c>
       <c r="N12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O12">
         <v>1.57</v>
@@ -1970,16 +1967,16 @@
         <v>6.5</v>
       </c>
       <c r="Z12">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AA12">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AB12">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC12">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD12">
         <v>4.1</v>
@@ -1988,7 +1985,7 @@
         <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG12">
         <v>1.67</v>
@@ -1997,13 +1994,13 @@
         <v>9.5</v>
       </c>
       <c r="AI12">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AJ12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL12" s="3">
         <v>45867.89930555555</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -163,12 +163,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -190,21 +190,21 @@
     <t>Dynamo Kyiv</t>
   </si>
   <si>
+    <t>Red Star Belgrade</t>
+  </si>
+  <si>
     <t>Zrinjski</t>
   </si>
   <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Criciúma</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
@@ -223,19 +223,19 @@
     <t>Hamrun Spartans</t>
   </si>
   <si>
+    <t>Lincoln Red Imps</t>
+  </si>
+  <si>
     <t>Slovan Bratislava</t>
   </si>
   <si>
-    <t>Lincoln Red Imps</t>
-  </si>
-  <si>
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -1229,76 +1229,76 @@
         <v>76</v>
       </c>
       <c r="L6">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M6">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N6">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O6">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="P6">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>7.3</v>
       </c>
       <c r="R6">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="S6">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="U6">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="V6">
-        <v>6.35</v>
+        <v>3.5</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AA6">
-        <v>3.48</v>
+        <v>7.1</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AC6">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE6">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF6">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="AG6">
-        <v>2.09</v>
+        <v>1.42</v>
       </c>
       <c r="AH6">
-        <v>5.65</v>
+        <v>2.74</v>
       </c>
       <c r="AI6">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AJ6" t="s">
         <v>77</v>
@@ -1345,76 +1345,76 @@
         <v>76</v>
       </c>
       <c r="L7">
+        <v>2.75</v>
+      </c>
+      <c r="M7">
+        <v>3.4</v>
+      </c>
+      <c r="N7">
+        <v>2.42</v>
+      </c>
+      <c r="O7">
+        <v>2.02</v>
+      </c>
+      <c r="P7">
+        <v>11.5</v>
+      </c>
+      <c r="Q7">
+        <v>1.96</v>
+      </c>
+      <c r="R7">
+        <v>1.35</v>
+      </c>
+      <c r="S7">
+        <v>2.84</v>
+      </c>
+      <c r="T7">
+        <v>2.6</v>
+      </c>
+      <c r="U7">
+        <v>1.41</v>
+      </c>
+      <c r="V7">
+        <v>6.35</v>
+      </c>
+      <c r="W7">
         <v>1.06</v>
       </c>
-      <c r="M7">
-        <v>11</v>
-      </c>
-      <c r="N7">
-        <v>28</v>
-      </c>
-      <c r="O7">
-        <v>1.07</v>
-      </c>
-      <c r="P7">
-        <v>46</v>
-      </c>
-      <c r="Q7">
-        <v>7.3</v>
-      </c>
-      <c r="R7">
-        <v>1.1</v>
-      </c>
-      <c r="S7">
-        <v>5.1</v>
-      </c>
-      <c r="T7">
-        <v>1.82</v>
-      </c>
-      <c r="U7">
-        <v>1.88</v>
-      </c>
-      <c r="V7">
-        <v>3.5</v>
-      </c>
-      <c r="W7">
-        <v>1.22</v>
-      </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z7">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AA7">
-        <v>7.1</v>
+        <v>3.48</v>
       </c>
       <c r="AB7">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD7">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="AE7">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF7">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG7">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AH7">
-        <v>2.74</v>
+        <v>5.65</v>
       </c>
       <c r="AI7">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
         <v>77</v>
@@ -1464,10 +1464,10 @@
         <v>1.5</v>
       </c>
       <c r="M8">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="N8">
-        <v>5.32</v>
+        <v>5.8</v>
       </c>
       <c r="O8">
         <v>1.5</v>
@@ -1500,7 +1500,7 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z8">
         <v>1.3</v>
@@ -1524,10 +1524,10 @@
         <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH8">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AI8">
         <v>1.09</v>
@@ -1577,76 +1577,76 @@
         <v>76</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M9">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="N9">
+        <v>3.03</v>
+      </c>
+      <c r="O9">
+        <v>1.85</v>
+      </c>
+      <c r="P9">
+        <v>8</v>
+      </c>
+      <c r="Q9">
+        <v>2.25</v>
+      </c>
+      <c r="R9">
+        <v>1.48</v>
+      </c>
+      <c r="S9">
+        <v>2.5</v>
+      </c>
+      <c r="T9">
+        <v>3</v>
+      </c>
+      <c r="U9">
+        <v>1.33</v>
+      </c>
+      <c r="V9">
+        <v>6.8</v>
+      </c>
+      <c r="W9">
+        <v>1.03</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>7.3</v>
+      </c>
+      <c r="Z9">
+        <v>1.38</v>
+      </c>
+      <c r="AA9">
+        <v>3.04</v>
+      </c>
+      <c r="AB9">
+        <v>2.06</v>
+      </c>
+      <c r="AC9">
+        <v>1.73</v>
+      </c>
+      <c r="AD9">
         <v>4</v>
       </c>
-      <c r="O9">
-        <v>1.77</v>
-      </c>
-      <c r="P9">
-        <v>6.5</v>
-      </c>
-      <c r="Q9">
-        <v>2.65</v>
-      </c>
-      <c r="R9">
-        <v>1.56</v>
-      </c>
-      <c r="S9">
-        <v>2.15</v>
-      </c>
-      <c r="T9">
-        <v>3.55</v>
-      </c>
-      <c r="U9">
-        <v>1.25</v>
-      </c>
-      <c r="V9">
-        <v>11</v>
-      </c>
-      <c r="W9">
-        <v>1.01</v>
-      </c>
-      <c r="X9">
-        <v>1.09</v>
-      </c>
-      <c r="Y9">
-        <v>6</v>
-      </c>
-      <c r="Z9">
-        <v>1.52</v>
-      </c>
-      <c r="AA9">
-        <v>2.47</v>
-      </c>
-      <c r="AB9">
-        <v>2.6</v>
-      </c>
-      <c r="AC9">
-        <v>1.44</v>
-      </c>
-      <c r="AD9">
-        <v>5</v>
-      </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF9">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AH9">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AI9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ9" t="s">
         <v>77</v>
@@ -1693,76 +1693,76 @@
         <v>76</v>
       </c>
       <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>3</v>
+      </c>
+      <c r="N10">
+        <v>4.2</v>
+      </c>
+      <c r="O10">
+        <v>1.77</v>
+      </c>
+      <c r="P10">
+        <v>6.5</v>
+      </c>
+      <c r="Q10">
+        <v>2.65</v>
+      </c>
+      <c r="R10">
+        <v>1.6</v>
+      </c>
+      <c r="S10">
         <v>2.15</v>
       </c>
-      <c r="M10">
-        <v>3.08</v>
-      </c>
-      <c r="N10">
-        <v>3.03</v>
-      </c>
-      <c r="O10">
-        <v>1.85</v>
-      </c>
-      <c r="P10">
-        <v>8</v>
-      </c>
-      <c r="Q10">
-        <v>2.25</v>
-      </c>
-      <c r="R10">
+      <c r="T10">
+        <v>3.4</v>
+      </c>
+      <c r="U10">
+        <v>1.25</v>
+      </c>
+      <c r="V10">
+        <v>7.8</v>
+      </c>
+      <c r="W10">
+        <v>1.02</v>
+      </c>
+      <c r="X10">
+        <v>1.06</v>
+      </c>
+      <c r="Y10">
+        <v>6.2</v>
+      </c>
+      <c r="Z10">
+        <v>1.52</v>
+      </c>
+      <c r="AA10">
+        <v>2.47</v>
+      </c>
+      <c r="AB10">
+        <v>2.6</v>
+      </c>
+      <c r="AC10">
         <v>1.43</v>
       </c>
-      <c r="S10">
-        <v>2.54</v>
-      </c>
-      <c r="T10">
-        <v>3.29</v>
-      </c>
-      <c r="U10">
-        <v>1.32</v>
-      </c>
-      <c r="V10">
-        <v>7.4</v>
-      </c>
-      <c r="W10">
-        <v>1.03</v>
-      </c>
-      <c r="X10">
-        <v>1.05</v>
-      </c>
-      <c r="Y10">
-        <v>10</v>
-      </c>
-      <c r="Z10">
-        <v>1.36</v>
-      </c>
-      <c r="AA10">
-        <v>2.88</v>
-      </c>
-      <c r="AB10">
-        <v>2.09</v>
-      </c>
-      <c r="AC10">
-        <v>1.74</v>
-      </c>
       <c r="AD10">
-        <v>3.8</v>
+        <v>4.85</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AG10">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AH10">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AI10">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ10" t="s">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
@@ -1925,13 +1925,13 @@
         <v>76</v>
       </c>
       <c r="L12">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="M12">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="O12">
         <v>1.57</v>
@@ -1943,19 +1943,19 @@
         <v>3.1</v>
       </c>
       <c r="R12">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S12">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T12">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U12">
         <v>1.3</v>
       </c>
       <c r="V12">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="W12">
         <v>1.06</v>
@@ -1964,19 +1964,19 @@
         <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AA12">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AB12">
         <v>2.28</v>
       </c>
       <c r="AC12">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AD12">
         <v>4.1</v>
@@ -1991,10 +1991,10 @@
         <v>1.67</v>
       </c>
       <c r="AH12">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AI12">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
         <v>77</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -163,12 +163,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -199,12 +199,12 @@
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
     <t>Grêmio</t>
   </si>
   <si>
-    <t>Criciúma</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
@@ -232,10 +232,10 @@
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -1461,13 +1461,13 @@
         <v>76</v>
       </c>
       <c r="L8">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M8">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N8">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>1.5</v>
@@ -1479,58 +1479,58 @@
         <v>3</v>
       </c>
       <c r="R8">
+        <v>1.37</v>
+      </c>
+      <c r="S8">
+        <v>2.72</v>
+      </c>
+      <c r="T8">
+        <v>2.93</v>
+      </c>
+      <c r="U8">
         <v>1.4</v>
       </c>
-      <c r="S8">
-        <v>2.7</v>
-      </c>
-      <c r="T8">
-        <v>2.88</v>
-      </c>
-      <c r="U8">
-        <v>1.36</v>
-      </c>
       <c r="V8">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Z8">
         <v>1.3</v>
       </c>
       <c r="AA8">
-        <v>3.16</v>
+        <v>3.07</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC8">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AD8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE8">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF8">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AI8">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AJ8" t="s">
         <v>77</v>
@@ -1577,76 +1577,76 @@
         <v>76</v>
       </c>
       <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>3</v>
+      </c>
+      <c r="N9">
+        <v>4.2</v>
+      </c>
+      <c r="O9">
+        <v>1.77</v>
+      </c>
+      <c r="P9">
+        <v>6.5</v>
+      </c>
+      <c r="Q9">
+        <v>2.65</v>
+      </c>
+      <c r="R9">
+        <v>1.6</v>
+      </c>
+      <c r="S9">
         <v>2.15</v>
       </c>
-      <c r="M9">
-        <v>3.08</v>
-      </c>
-      <c r="N9">
-        <v>3.03</v>
-      </c>
-      <c r="O9">
-        <v>1.85</v>
-      </c>
-      <c r="P9">
-        <v>8</v>
-      </c>
-      <c r="Q9">
-        <v>2.25</v>
-      </c>
-      <c r="R9">
-        <v>1.48</v>
-      </c>
-      <c r="S9">
-        <v>2.5</v>
-      </c>
       <c r="T9">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V9">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="Z9">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AA9">
-        <v>3.04</v>
+        <v>2.47</v>
       </c>
       <c r="AB9">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="AC9">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AD9">
-        <v>4</v>
+        <v>4.85</v>
       </c>
       <c r="AE9">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AH9">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="AI9">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ9" t="s">
         <v>77</v>
@@ -1693,76 +1693,76 @@
         <v>76</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M10">
+        <v>3.08</v>
+      </c>
+      <c r="N10">
+        <v>3.03</v>
+      </c>
+      <c r="O10">
+        <v>1.85</v>
+      </c>
+      <c r="P10">
+        <v>8</v>
+      </c>
+      <c r="Q10">
+        <v>2.25</v>
+      </c>
+      <c r="R10">
+        <v>1.48</v>
+      </c>
+      <c r="S10">
+        <v>2.5</v>
+      </c>
+      <c r="T10">
         <v>3</v>
       </c>
-      <c r="N10">
-        <v>4.2</v>
-      </c>
-      <c r="O10">
-        <v>1.77</v>
-      </c>
-      <c r="P10">
-        <v>6.5</v>
-      </c>
-      <c r="Q10">
-        <v>2.65</v>
-      </c>
-      <c r="R10">
-        <v>1.6</v>
-      </c>
-      <c r="S10">
-        <v>2.15</v>
-      </c>
-      <c r="T10">
-        <v>3.4</v>
-      </c>
       <c r="U10">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V10">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
+        <v>1.03</v>
+      </c>
+      <c r="Y10">
+        <v>7.3</v>
+      </c>
+      <c r="Z10">
+        <v>1.38</v>
+      </c>
+      <c r="AA10">
+        <v>3.04</v>
+      </c>
+      <c r="AB10">
+        <v>2.06</v>
+      </c>
+      <c r="AC10">
+        <v>1.73</v>
+      </c>
+      <c r="AD10">
+        <v>4</v>
+      </c>
+      <c r="AE10">
+        <v>1.21</v>
+      </c>
+      <c r="AF10">
+        <v>1.85</v>
+      </c>
+      <c r="AG10">
+        <v>1.91</v>
+      </c>
+      <c r="AH10">
+        <v>8.5</v>
+      </c>
+      <c r="AI10">
         <v>1.06</v>
-      </c>
-      <c r="Y10">
-        <v>6.2</v>
-      </c>
-      <c r="Z10">
-        <v>1.52</v>
-      </c>
-      <c r="AA10">
-        <v>2.47</v>
-      </c>
-      <c r="AB10">
-        <v>2.6</v>
-      </c>
-      <c r="AC10">
-        <v>1.43</v>
-      </c>
-      <c r="AD10">
-        <v>4.85</v>
-      </c>
-      <c r="AE10">
-        <v>1.11</v>
-      </c>
-      <c r="AF10">
-        <v>2.19</v>
-      </c>
-      <c r="AG10">
-        <v>1.62</v>
-      </c>
-      <c r="AH10">
-        <v>11.5</v>
-      </c>
-      <c r="AI10">
-        <v>1.01</v>
       </c>
       <c r="AJ10" t="s">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -184,18 +184,18 @@
     <t>Kairat</t>
   </si>
   <si>
+    <t>Dynamo Kyiv</t>
+  </si>
+  <si>
     <t>Drita</t>
   </si>
   <si>
-    <t>Dynamo Kyiv</t>
+    <t>Zrinjski</t>
   </si>
   <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
@@ -217,16 +217,16 @@
     <t>KuPS</t>
   </si>
   <si>
+    <t>Hamrun Spartans</t>
+  </si>
+  <si>
     <t>København</t>
   </si>
   <si>
-    <t>Hamrun Spartans</t>
+    <t>Slovan Bratislava</t>
   </si>
   <si>
     <t>Lincoln Red Imps</t>
-  </si>
-  <si>
-    <t>Slovan Bratislava</t>
   </si>
   <si>
     <t>Miami FC II</t>
@@ -997,76 +997,76 @@
         <v>76</v>
       </c>
       <c r="L4">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M4">
+        <v>6.5</v>
+      </c>
+      <c r="N4">
+        <v>13</v>
+      </c>
+      <c r="O4">
+        <v>1.18</v>
+      </c>
+      <c r="P4">
+        <v>19.5</v>
+      </c>
+      <c r="Q4">
+        <v>5.2</v>
+      </c>
+      <c r="R4">
+        <v>1.2</v>
+      </c>
+      <c r="S4">
+        <v>3.72</v>
+      </c>
+      <c r="T4">
+        <v>2.12</v>
+      </c>
+      <c r="U4">
+        <v>1.64</v>
+      </c>
+      <c r="V4">
         <v>4.6</v>
       </c>
-      <c r="N4">
-        <v>1.39</v>
-      </c>
-      <c r="O4">
-        <v>3.25</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>1.4</v>
-      </c>
-      <c r="R4">
-        <v>1.33</v>
-      </c>
-      <c r="S4">
-        <v>3.25</v>
-      </c>
-      <c r="T4">
-        <v>2.63</v>
-      </c>
-      <c r="U4">
-        <v>1.44</v>
-      </c>
-      <c r="V4">
-        <v>6</v>
-      </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB4">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AC4">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG4">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ4" t="s">
         <v>77</v>
@@ -1113,76 +1113,76 @@
         <v>76</v>
       </c>
       <c r="L5">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M5">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N5">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O5">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U5">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V5">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD5">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH5">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
         <v>77</v>
@@ -1229,76 +1229,76 @@
         <v>76</v>
       </c>
       <c r="L6">
+        <v>2.75</v>
+      </c>
+      <c r="M6">
+        <v>3.4</v>
+      </c>
+      <c r="N6">
+        <v>2.42</v>
+      </c>
+      <c r="O6">
+        <v>2.02</v>
+      </c>
+      <c r="P6">
+        <v>11.5</v>
+      </c>
+      <c r="Q6">
+        <v>1.96</v>
+      </c>
+      <c r="R6">
+        <v>1.35</v>
+      </c>
+      <c r="S6">
+        <v>2.84</v>
+      </c>
+      <c r="T6">
+        <v>2.6</v>
+      </c>
+      <c r="U6">
+        <v>1.41</v>
+      </c>
+      <c r="V6">
+        <v>6.35</v>
+      </c>
+      <c r="W6">
         <v>1.06</v>
       </c>
-      <c r="M6">
-        <v>11</v>
-      </c>
-      <c r="N6">
-        <v>28</v>
-      </c>
-      <c r="O6">
-        <v>1.07</v>
-      </c>
-      <c r="P6">
-        <v>46</v>
-      </c>
-      <c r="Q6">
-        <v>7.3</v>
-      </c>
-      <c r="R6">
-        <v>1.1</v>
-      </c>
-      <c r="S6">
-        <v>5.1</v>
-      </c>
-      <c r="T6">
-        <v>1.82</v>
-      </c>
-      <c r="U6">
-        <v>1.88</v>
-      </c>
-      <c r="V6">
-        <v>3.5</v>
-      </c>
-      <c r="W6">
-        <v>1.22</v>
-      </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z6">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AA6">
-        <v>7.1</v>
+        <v>3.48</v>
       </c>
       <c r="AB6">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD6">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="AE6">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF6">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG6">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AH6">
-        <v>2.74</v>
+        <v>5.65</v>
       </c>
       <c r="AI6">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="s">
         <v>77</v>
@@ -1345,76 +1345,76 @@
         <v>76</v>
       </c>
       <c r="L7">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M7">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N7">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O7">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="P7">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="Q7">
-        <v>1.96</v>
+        <v>7.3</v>
       </c>
       <c r="R7">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="S7">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="T7">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="U7">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="V7">
-        <v>6.35</v>
+        <v>3.5</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AA7">
-        <v>3.48</v>
+        <v>7.1</v>
       </c>
       <c r="AB7">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AC7">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="AD7">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE7">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF7">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="AG7">
-        <v>2.09</v>
+        <v>1.42</v>
       </c>
       <c r="AH7">
-        <v>5.65</v>
+        <v>2.74</v>
       </c>
       <c r="AI7">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AJ7" t="s">
         <v>77</v>
@@ -1583,7 +1583,7 @@
         <v>3</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="O9">
         <v>1.77</v>
@@ -1610,43 +1610,43 @@
         <v>7.8</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
         <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="Z9">
         <v>1.52</v>
       </c>
       <c r="AA9">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="AB9">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC9">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AD9">
         <v>4.85</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH9">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ9" t="s">
         <v>77</v>
@@ -1711,40 +1711,40 @@
         <v>2.25</v>
       </c>
       <c r="R10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S10">
         <v>2.5</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V10">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y10">
         <v>7.3</v>
       </c>
       <c r="Z10">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AA10">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AB10">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AD10">
         <v>4</v>
@@ -1759,10 +1759,10 @@
         <v>1.91</v>
       </c>
       <c r="AH10">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="AI10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AJ10" t="s">
         <v>77</v>
@@ -1964,13 +1964,13 @@
         <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z12">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AA12">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AB12">
         <v>2.28</v>
@@ -1982,7 +1982,7 @@
         <v>4.1</v>
       </c>
       <c r="AE12">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
         <v>2.1</v>
@@ -1991,10 +1991,10 @@
         <v>1.67</v>
       </c>
       <c r="AH12">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AI12">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ12" t="s">
         <v>77</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -163,12 +163,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -184,12 +184,12 @@
     <t>Kairat</t>
   </si>
   <si>
+    <t>Drita</t>
+  </si>
+  <si>
     <t>Dynamo Kyiv</t>
   </si>
   <si>
-    <t>Drita</t>
-  </si>
-  <si>
     <t>Zrinjski</t>
   </si>
   <si>
@@ -199,12 +199,12 @@
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Criciúma</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
@@ -217,12 +217,12 @@
     <t>KuPS</t>
   </si>
   <si>
+    <t>København</t>
+  </si>
+  <si>
     <t>Hamrun Spartans</t>
   </si>
   <si>
-    <t>København</t>
-  </si>
-  <si>
     <t>Slovan Bratislava</t>
   </si>
   <si>
@@ -232,10 +232,10 @@
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -997,76 +997,76 @@
         <v>76</v>
       </c>
       <c r="L4">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M4">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N4">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O4">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U4">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V4">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD4">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG4">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH4">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="s">
         <v>77</v>
@@ -1113,76 +1113,76 @@
         <v>76</v>
       </c>
       <c r="L5">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M5">
+        <v>6.5</v>
+      </c>
+      <c r="N5">
+        <v>13</v>
+      </c>
+      <c r="O5">
+        <v>1.18</v>
+      </c>
+      <c r="P5">
+        <v>19.5</v>
+      </c>
+      <c r="Q5">
+        <v>5.2</v>
+      </c>
+      <c r="R5">
+        <v>1.2</v>
+      </c>
+      <c r="S5">
+        <v>3.72</v>
+      </c>
+      <c r="T5">
+        <v>2.12</v>
+      </c>
+      <c r="U5">
+        <v>1.64</v>
+      </c>
+      <c r="V5">
         <v>4.6</v>
       </c>
-      <c r="N5">
-        <v>1.39</v>
-      </c>
-      <c r="O5">
-        <v>3.25</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>1.4</v>
-      </c>
-      <c r="R5">
-        <v>1.33</v>
-      </c>
-      <c r="S5">
-        <v>3.25</v>
-      </c>
-      <c r="T5">
-        <v>2.63</v>
-      </c>
-      <c r="U5">
-        <v>1.44</v>
-      </c>
-      <c r="V5">
-        <v>6</v>
-      </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AC5">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG5">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ5" t="s">
         <v>77</v>
@@ -1577,76 +1577,76 @@
         <v>76</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N9">
-        <v>4.19</v>
+        <v>3.03</v>
       </c>
       <c r="O9">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P9">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R9">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S9">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="T9">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="U9">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y9">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="Z9">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AA9">
-        <v>2.53</v>
+        <v>3.25</v>
       </c>
       <c r="AB9">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="AC9">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="AD9">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AH9">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AI9">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AJ9" t="s">
         <v>77</v>
@@ -1693,76 +1693,76 @@
         <v>76</v>
       </c>
       <c r="L10">
+        <v>1.95</v>
+      </c>
+      <c r="M10">
+        <v>2.9</v>
+      </c>
+      <c r="N10">
+        <v>3.81</v>
+      </c>
+      <c r="O10">
+        <v>1.77</v>
+      </c>
+      <c r="P10">
+        <v>6.5</v>
+      </c>
+      <c r="Q10">
+        <v>2.65</v>
+      </c>
+      <c r="R10">
+        <v>1.6</v>
+      </c>
+      <c r="S10">
         <v>2.15</v>
       </c>
-      <c r="M10">
-        <v>3.08</v>
-      </c>
-      <c r="N10">
-        <v>3.03</v>
-      </c>
-      <c r="O10">
-        <v>1.85</v>
-      </c>
-      <c r="P10">
-        <v>8</v>
-      </c>
-      <c r="Q10">
-        <v>2.25</v>
-      </c>
-      <c r="R10">
-        <v>1.5</v>
-      </c>
-      <c r="S10">
-        <v>2.5</v>
-      </c>
       <c r="T10">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="U10">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="Z10">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AA10">
-        <v>3.25</v>
+        <v>2.37</v>
       </c>
       <c r="AB10">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC10">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AD10">
-        <v>4</v>
+        <v>4.85</v>
       </c>
       <c r="AE10">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AH10">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AI10">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ10" t="s">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
@@ -1925,13 +1925,13 @@
         <v>76</v>
       </c>
       <c r="L12">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="M12">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="N12">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>1.57</v>
@@ -1973,10 +1973,10 @@
         <v>2.65</v>
       </c>
       <c r="AB12">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC12">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AD12">
         <v>4.1</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -163,12 +163,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -184,27 +184,27 @@
     <t>Kairat</t>
   </si>
   <si>
+    <t>Dynamo Kyiv</t>
+  </si>
+  <si>
     <t>Drita</t>
   </si>
   <si>
-    <t>Dynamo Kyiv</t>
+    <t>Red Star Belgrade</t>
   </si>
   <si>
     <t>Zrinjski</t>
   </si>
   <si>
-    <t>Red Star Belgrade</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
     <t>Grêmio</t>
   </si>
   <si>
-    <t>Criciúma</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
@@ -217,25 +217,25 @@
     <t>KuPS</t>
   </si>
   <si>
+    <t>Hamrun Spartans</t>
+  </si>
+  <si>
     <t>København</t>
   </si>
   <si>
-    <t>Hamrun Spartans</t>
+    <t>Lincoln Red Imps</t>
   </si>
   <si>
     <t>Slovan Bratislava</t>
   </si>
   <si>
-    <t>Lincoln Red Imps</t>
-  </si>
-  <si>
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
     <t>Fortaleza</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -997,76 +997,76 @@
         <v>76</v>
       </c>
       <c r="L4">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M4">
+        <v>6.5</v>
+      </c>
+      <c r="N4">
+        <v>13</v>
+      </c>
+      <c r="O4">
+        <v>1.18</v>
+      </c>
+      <c r="P4">
+        <v>19.5</v>
+      </c>
+      <c r="Q4">
+        <v>5.2</v>
+      </c>
+      <c r="R4">
+        <v>1.2</v>
+      </c>
+      <c r="S4">
+        <v>3.72</v>
+      </c>
+      <c r="T4">
+        <v>2.12</v>
+      </c>
+      <c r="U4">
+        <v>1.64</v>
+      </c>
+      <c r="V4">
         <v>4.6</v>
       </c>
-      <c r="N4">
-        <v>1.39</v>
-      </c>
-      <c r="O4">
-        <v>3.25</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>1.4</v>
-      </c>
-      <c r="R4">
-        <v>1.33</v>
-      </c>
-      <c r="S4">
-        <v>3.25</v>
-      </c>
-      <c r="T4">
-        <v>2.63</v>
-      </c>
-      <c r="U4">
-        <v>1.44</v>
-      </c>
-      <c r="V4">
-        <v>6</v>
-      </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB4">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AC4">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG4">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ4" t="s">
         <v>77</v>
@@ -1113,76 +1113,76 @@
         <v>76</v>
       </c>
       <c r="L5">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M5">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N5">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O5">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U5">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V5">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD5">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH5">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
         <v>77</v>
@@ -1229,76 +1229,76 @@
         <v>76</v>
       </c>
       <c r="L6">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M6">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="N6">
-        <v>2.42</v>
+        <v>28</v>
       </c>
       <c r="O6">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="P6">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="Q6">
-        <v>1.96</v>
+        <v>7.3</v>
       </c>
       <c r="R6">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="S6">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="U6">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="V6">
-        <v>6.35</v>
+        <v>3.5</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="AA6">
-        <v>3.48</v>
+        <v>7.1</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AC6">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE6">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF6">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="AG6">
-        <v>2.09</v>
+        <v>1.42</v>
       </c>
       <c r="AH6">
-        <v>5.65</v>
+        <v>2.74</v>
       </c>
       <c r="AI6">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AJ6" t="s">
         <v>77</v>
@@ -1345,76 +1345,76 @@
         <v>76</v>
       </c>
       <c r="L7">
+        <v>2.75</v>
+      </c>
+      <c r="M7">
+        <v>3.4</v>
+      </c>
+      <c r="N7">
+        <v>2.42</v>
+      </c>
+      <c r="O7">
+        <v>2.02</v>
+      </c>
+      <c r="P7">
+        <v>11.5</v>
+      </c>
+      <c r="Q7">
+        <v>1.96</v>
+      </c>
+      <c r="R7">
+        <v>1.35</v>
+      </c>
+      <c r="S7">
+        <v>2.84</v>
+      </c>
+      <c r="T7">
+        <v>2.6</v>
+      </c>
+      <c r="U7">
+        <v>1.41</v>
+      </c>
+      <c r="V7">
+        <v>6.35</v>
+      </c>
+      <c r="W7">
         <v>1.06</v>
       </c>
-      <c r="M7">
-        <v>11</v>
-      </c>
-      <c r="N7">
-        <v>28</v>
-      </c>
-      <c r="O7">
-        <v>1.07</v>
-      </c>
-      <c r="P7">
-        <v>46</v>
-      </c>
-      <c r="Q7">
-        <v>7.3</v>
-      </c>
-      <c r="R7">
-        <v>1.1</v>
-      </c>
-      <c r="S7">
-        <v>5.1</v>
-      </c>
-      <c r="T7">
-        <v>1.82</v>
-      </c>
-      <c r="U7">
-        <v>1.88</v>
-      </c>
-      <c r="V7">
-        <v>3.5</v>
-      </c>
-      <c r="W7">
-        <v>1.22</v>
-      </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z7">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AA7">
-        <v>7.1</v>
+        <v>3.48</v>
       </c>
       <c r="AB7">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD7">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="AE7">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF7">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG7">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AH7">
-        <v>2.74</v>
+        <v>5.65</v>
       </c>
       <c r="AI7">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
         <v>77</v>
@@ -1577,76 +1577,76 @@
         <v>76</v>
       </c>
       <c r="L9">
+        <v>1.95</v>
+      </c>
+      <c r="M9">
+        <v>2.9</v>
+      </c>
+      <c r="N9">
+        <v>3.81</v>
+      </c>
+      <c r="O9">
+        <v>1.77</v>
+      </c>
+      <c r="P9">
+        <v>6.5</v>
+      </c>
+      <c r="Q9">
+        <v>2.65</v>
+      </c>
+      <c r="R9">
+        <v>1.6</v>
+      </c>
+      <c r="S9">
         <v>2.15</v>
       </c>
-      <c r="M9">
-        <v>3.08</v>
-      </c>
-      <c r="N9">
-        <v>3.03</v>
-      </c>
-      <c r="O9">
-        <v>1.85</v>
-      </c>
-      <c r="P9">
-        <v>8</v>
-      </c>
-      <c r="Q9">
-        <v>2.25</v>
-      </c>
-      <c r="R9">
-        <v>1.5</v>
-      </c>
-      <c r="S9">
-        <v>2.5</v>
-      </c>
       <c r="T9">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="Z9">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AA9">
-        <v>3.25</v>
+        <v>2.37</v>
       </c>
       <c r="AB9">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="AC9">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="AD9">
-        <v>4</v>
+        <v>4.85</v>
       </c>
       <c r="AE9">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AH9">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AI9">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ9" t="s">
         <v>77</v>
@@ -1693,76 +1693,76 @@
         <v>76</v>
       </c>
       <c r="L10">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M10">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N10">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O10">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P10">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S10">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="T10">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="U10">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y10">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="Z10">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AA10">
-        <v>2.37</v>
+        <v>3.25</v>
       </c>
       <c r="AB10">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="AC10">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="AD10">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AH10">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="AI10">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AJ10" t="s">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -163,12 +163,12 @@
     <t>USA USL Championship</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -184,27 +184,27 @@
     <t>Kairat</t>
   </si>
   <si>
+    <t>Drita</t>
+  </si>
+  <si>
     <t>Dynamo Kyiv</t>
   </si>
   <si>
-    <t>Drita</t>
+    <t>Zrinjski</t>
   </si>
   <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
     <t>Pittsburgh Riverhounds</t>
   </si>
   <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
     <t>Criciúma</t>
   </si>
   <si>
-    <t>Grêmio</t>
-  </si>
-  <si>
     <t>Valour FC</t>
   </si>
   <si>
@@ -217,25 +217,25 @@
     <t>KuPS</t>
   </si>
   <si>
+    <t>København</t>
+  </si>
+  <si>
     <t>Hamrun Spartans</t>
   </si>
   <si>
-    <t>København</t>
+    <t>Slovan Bratislava</t>
   </si>
   <si>
     <t>Lincoln Red Imps</t>
   </si>
   <si>
-    <t>Slovan Bratislava</t>
-  </si>
-  <si>
     <t>Miami FC II</t>
   </si>
   <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
     <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Fortaleza</t>
   </si>
   <si>
     <t>Cavalry FC</t>
@@ -997,76 +997,76 @@
         <v>76</v>
       </c>
       <c r="L4">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M4">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N4">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O4">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U4">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V4">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD4">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG4">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH4">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="s">
         <v>77</v>
@@ -1113,76 +1113,76 @@
         <v>76</v>
       </c>
       <c r="L5">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M5">
+        <v>6.5</v>
+      </c>
+      <c r="N5">
+        <v>13</v>
+      </c>
+      <c r="O5">
+        <v>1.18</v>
+      </c>
+      <c r="P5">
+        <v>19.5</v>
+      </c>
+      <c r="Q5">
+        <v>5.2</v>
+      </c>
+      <c r="R5">
+        <v>1.2</v>
+      </c>
+      <c r="S5">
+        <v>3.72</v>
+      </c>
+      <c r="T5">
+        <v>2.12</v>
+      </c>
+      <c r="U5">
+        <v>1.64</v>
+      </c>
+      <c r="V5">
         <v>4.6</v>
       </c>
-      <c r="N5">
-        <v>1.39</v>
-      </c>
-      <c r="O5">
-        <v>3.25</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>1.4</v>
-      </c>
-      <c r="R5">
-        <v>1.33</v>
-      </c>
-      <c r="S5">
-        <v>3.25</v>
-      </c>
-      <c r="T5">
-        <v>2.63</v>
-      </c>
-      <c r="U5">
-        <v>1.44</v>
-      </c>
-      <c r="V5">
-        <v>6</v>
-      </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AC5">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG5">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ5" t="s">
         <v>77</v>
@@ -1229,76 +1229,76 @@
         <v>76</v>
       </c>
       <c r="L6">
+        <v>2.75</v>
+      </c>
+      <c r="M6">
+        <v>3.4</v>
+      </c>
+      <c r="N6">
+        <v>2.42</v>
+      </c>
+      <c r="O6">
+        <v>2.02</v>
+      </c>
+      <c r="P6">
+        <v>11.5</v>
+      </c>
+      <c r="Q6">
+        <v>1.96</v>
+      </c>
+      <c r="R6">
+        <v>1.35</v>
+      </c>
+      <c r="S6">
+        <v>2.84</v>
+      </c>
+      <c r="T6">
+        <v>2.6</v>
+      </c>
+      <c r="U6">
+        <v>1.41</v>
+      </c>
+      <c r="V6">
+        <v>6.35</v>
+      </c>
+      <c r="W6">
         <v>1.06</v>
       </c>
-      <c r="M6">
-        <v>11</v>
-      </c>
-      <c r="N6">
-        <v>28</v>
-      </c>
-      <c r="O6">
-        <v>1.07</v>
-      </c>
-      <c r="P6">
-        <v>46</v>
-      </c>
-      <c r="Q6">
-        <v>7.3</v>
-      </c>
-      <c r="R6">
-        <v>1.1</v>
-      </c>
-      <c r="S6">
-        <v>5.1</v>
-      </c>
-      <c r="T6">
-        <v>1.82</v>
-      </c>
-      <c r="U6">
-        <v>1.88</v>
-      </c>
-      <c r="V6">
-        <v>3.5</v>
-      </c>
-      <c r="W6">
-        <v>1.22</v>
-      </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z6">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AA6">
-        <v>7.1</v>
+        <v>3.48</v>
       </c>
       <c r="AB6">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD6">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="AE6">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF6">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG6">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AH6">
-        <v>2.74</v>
+        <v>5.65</v>
       </c>
       <c r="AI6">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AJ6" t="s">
         <v>77</v>
@@ -1345,76 +1345,76 @@
         <v>76</v>
       </c>
       <c r="L7">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M7">
+        <v>11</v>
+      </c>
+      <c r="N7">
+        <v>28</v>
+      </c>
+      <c r="O7">
+        <v>1.07</v>
+      </c>
+      <c r="P7">
+        <v>46</v>
+      </c>
+      <c r="Q7">
+        <v>7.3</v>
+      </c>
+      <c r="R7">
+        <v>1.1</v>
+      </c>
+      <c r="S7">
+        <v>5.1</v>
+      </c>
+      <c r="T7">
+        <v>1.82</v>
+      </c>
+      <c r="U7">
+        <v>1.88</v>
+      </c>
+      <c r="V7">
+        <v>3.5</v>
+      </c>
+      <c r="W7">
+        <v>1.22</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>11</v>
+      </c>
+      <c r="Z7">
+        <v>1.04</v>
+      </c>
+      <c r="AA7">
+        <v>7.1</v>
+      </c>
+      <c r="AB7">
+        <v>1.29</v>
+      </c>
+      <c r="AC7">
         <v>3.4</v>
       </c>
-      <c r="N7">
-        <v>2.42</v>
-      </c>
-      <c r="O7">
-        <v>2.02</v>
-      </c>
-      <c r="P7">
-        <v>11.5</v>
-      </c>
-      <c r="Q7">
-        <v>1.96</v>
-      </c>
-      <c r="R7">
-        <v>1.35</v>
-      </c>
-      <c r="S7">
-        <v>2.84</v>
-      </c>
-      <c r="T7">
-        <v>2.6</v>
-      </c>
-      <c r="U7">
-        <v>1.41</v>
-      </c>
-      <c r="V7">
-        <v>6.35</v>
-      </c>
-      <c r="W7">
-        <v>1.06</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z7">
-        <v>1.24</v>
-      </c>
-      <c r="AA7">
-        <v>3.48</v>
-      </c>
-      <c r="AB7">
-        <v>1.8</v>
-      </c>
-      <c r="AC7">
-        <v>1.91</v>
-      </c>
       <c r="AD7">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE7">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF7">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="AG7">
-        <v>2.09</v>
+        <v>1.42</v>
       </c>
       <c r="AH7">
-        <v>5.65</v>
+        <v>2.74</v>
       </c>
       <c r="AI7">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AJ7" t="s">
         <v>77</v>
@@ -1461,13 +1461,13 @@
         <v>76</v>
       </c>
       <c r="L8">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="O8">
         <v>1.5</v>
@@ -1479,40 +1479,40 @@
         <v>3</v>
       </c>
       <c r="R8">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="T8">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V8">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
         <v>8.5</v>
       </c>
       <c r="Z8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AA8">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="AB8">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AC8">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AD8">
         <v>3.5</v>
@@ -1521,16 +1521,16 @@
         <v>1.25</v>
       </c>
       <c r="AF8">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AG8">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AH8">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AI8">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ8" t="s">
         <v>77</v>
@@ -1577,76 +1577,76 @@
         <v>76</v>
       </c>
       <c r="L9">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M9">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N9">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O9">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P9">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R9">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="S9">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="T9">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
+        <v>1.08</v>
+      </c>
+      <c r="Y9">
+        <v>8</v>
+      </c>
+      <c r="Z9">
+        <v>1.35</v>
+      </c>
+      <c r="AA9">
+        <v>2.83</v>
+      </c>
+      <c r="AB9">
+        <v>2.2</v>
+      </c>
+      <c r="AC9">
+        <v>1.61</v>
+      </c>
+      <c r="AD9">
+        <v>4</v>
+      </c>
+      <c r="AE9">
+        <v>1.22</v>
+      </c>
+      <c r="AF9">
+        <v>1.92</v>
+      </c>
+      <c r="AG9">
+        <v>1.88</v>
+      </c>
+      <c r="AH9">
+        <v>7.2</v>
+      </c>
+      <c r="AI9">
         <v>1.06</v>
-      </c>
-      <c r="Y9">
-        <v>7.5</v>
-      </c>
-      <c r="Z9">
-        <v>1.48</v>
-      </c>
-      <c r="AA9">
-        <v>2.37</v>
-      </c>
-      <c r="AB9">
-        <v>2.55</v>
-      </c>
-      <c r="AC9">
-        <v>1.45</v>
-      </c>
-      <c r="AD9">
-        <v>4.85</v>
-      </c>
-      <c r="AE9">
-        <v>1.14</v>
-      </c>
-      <c r="AF9">
-        <v>2.1</v>
-      </c>
-      <c r="AG9">
-        <v>1.57</v>
-      </c>
-      <c r="AH9">
-        <v>10</v>
-      </c>
-      <c r="AI9">
-        <v>1.04</v>
       </c>
       <c r="AJ9" t="s">
         <v>77</v>
@@ -1693,76 +1693,76 @@
         <v>76</v>
       </c>
       <c r="L10">
+        <v>1.95</v>
+      </c>
+      <c r="M10">
+        <v>2.9</v>
+      </c>
+      <c r="N10">
+        <v>3.81</v>
+      </c>
+      <c r="O10">
+        <v>1.77</v>
+      </c>
+      <c r="P10">
+        <v>6.5</v>
+      </c>
+      <c r="Q10">
+        <v>2.65</v>
+      </c>
+      <c r="R10">
+        <v>1.6</v>
+      </c>
+      <c r="S10">
         <v>2.15</v>
       </c>
-      <c r="M10">
-        <v>3.08</v>
-      </c>
-      <c r="N10">
-        <v>3.03</v>
-      </c>
-      <c r="O10">
-        <v>1.85</v>
-      </c>
-      <c r="P10">
-        <v>8</v>
-      </c>
-      <c r="Q10">
+      <c r="T10">
+        <v>3.4</v>
+      </c>
+      <c r="U10">
+        <v>1.25</v>
+      </c>
+      <c r="V10">
+        <v>7.8</v>
+      </c>
+      <c r="W10">
+        <v>1.04</v>
+      </c>
+      <c r="X10">
+        <v>1.09</v>
+      </c>
+      <c r="Y10">
+        <v>6</v>
+      </c>
+      <c r="Z10">
+        <v>1.48</v>
+      </c>
+      <c r="AA10">
+        <v>2.37</v>
+      </c>
+      <c r="AB10">
+        <v>2.47</v>
+      </c>
+      <c r="AC10">
+        <v>1.48</v>
+      </c>
+      <c r="AD10">
+        <v>5.25</v>
+      </c>
+      <c r="AE10">
+        <v>1.14</v>
+      </c>
+      <c r="AF10">
         <v>2.25</v>
       </c>
-      <c r="R10">
-        <v>1.5</v>
-      </c>
-      <c r="S10">
-        <v>2.5</v>
-      </c>
-      <c r="T10">
-        <v>2.98</v>
-      </c>
-      <c r="U10">
-        <v>1.32</v>
-      </c>
-      <c r="V10">
-        <v>8</v>
-      </c>
-      <c r="W10">
-        <v>1.03</v>
-      </c>
-      <c r="X10">
-        <v>1.08</v>
-      </c>
-      <c r="Y10">
-        <v>7.3</v>
-      </c>
-      <c r="Z10">
-        <v>1.32</v>
-      </c>
-      <c r="AA10">
-        <v>3.25</v>
-      </c>
-      <c r="AB10">
-        <v>2.09</v>
-      </c>
-      <c r="AC10">
-        <v>1.74</v>
-      </c>
-      <c r="AD10">
-        <v>4</v>
-      </c>
-      <c r="AE10">
-        <v>1.21</v>
-      </c>
-      <c r="AF10">
-        <v>1.85</v>
-      </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AH10">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="AI10">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ10" t="s">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
         <v>52</v>
@@ -1982,10 +1982,10 @@
         <v>4.1</v>
       </c>
       <c r="AE12">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG12">
         <v>1.67</v>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -912,12 +912,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -938,76 +938,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N5" t="n">
+        <v>13</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V5" t="n">
         <v>4.6</v>
       </c>
-      <c r="N5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.5</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH5" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,76 +1202,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>28</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P6" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC6" t="n">
         <v>3.4</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="P6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD6" t="n">
-        <v>3.02</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.09</v>
+        <v>1.42</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.65</v>
+        <v>2.35</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,76 +1334,76 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.06</v>
       </c>
-      <c r="M7" t="n">
-        <v>11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>28</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P7" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.1</v>
+        <v>3.48</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.35</v>
+        <v>5.65</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="M8" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>5.8</v>
+        <v>5.09</v>
       </c>
       <c r="O8" t="n">
         <v>1.5</v>
@@ -1490,13 +1490,13 @@
         <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="U8" t="n">
         <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
         <v>1.07</v>
@@ -1508,28 +1508,28 @@
         <v>8.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="n">
         <v>6.95</v>
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>3.38</v>
       </c>
       <c r="O9" t="n">
         <v>1.85</v>
@@ -1616,58 +1616,58 @@
         <v>2.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="T9" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA9" t="n">
         <v>2.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG9" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AH9" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.81</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>1.77</v>
@@ -1754,52 +1754,52 @@
         <v>2.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="W10" t="n">
         <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y10" t="n">
         <v>6</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AE10" t="n">
         <v>1.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AG10" t="n">
         <v>1.57</v>
       </c>
       <c r="AH10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1862,76 +1862,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>1.57</v>
@@ -2024,28 +2024,28 @@
         <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
         <v>7</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD12" t="n">
         <v>4.1</v>
@@ -2063,7 +2063,7 @@
         <v>8.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="M9" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.25</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.51</v>
-      </c>
       <c r="T9" t="n">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="V9" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.3</v>
+        <v>11.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P10" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="U10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.22</v>
       </c>
-      <c r="V10" t="n">
-        <v>12</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AH10" t="n">
-        <v>11.5</v>
+        <v>7.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>1.57</v>
@@ -2018,52 +2018,52 @@
         <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z12" t="n">
         <v>1.37</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AB12" t="n">
         <v>2.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AD12" t="n">
         <v>4.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH12" t="n">
         <v>8.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1598,76 +1598,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P9" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>2.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.3</v>
+        <v>3.72</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AH9" t="n">
-        <v>11.5</v>
+        <v>7.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.2</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.25</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T10" t="n">
-        <v>2.98</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="V10" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
         <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.72</v>
+        <v>5.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="n">
-        <v>7.75</v>
+        <v>11.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL12"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -657,7 +652,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -670,7 +665,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -713,28 +708,32 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['48', '54']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -745,17 +744,10 @@
       <c r="AI2" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45867.45833333334</v>
       </c>
     </row>
@@ -789,20 +781,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -815,13 +807,13 @@
         <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.89</v>
       </c>
       <c r="P3" t="n">
-        <v>14.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.68</v>
+        <v>6.95</v>
       </c>
       <c r="R3" t="n">
         <v>1.29</v>
@@ -836,58 +828,55 @@
         <v>1.43</v>
       </c>
       <c r="V3" t="n">
-        <v>6.55</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>3.84</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>1.77</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.2</v>
+        <v>1.93</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.84</v>
+        <v>2.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['9', '29', '43']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI3" t="n">
         <v>1.33</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AJ3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45867.5</v>
       </c>
     </row>
@@ -924,17 +913,17 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -947,13 +936,13 @@
         <v>1.39</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>10.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
@@ -968,58 +957,55 @@
         <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.5</v>
+        <v>1.75</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['42']</t>
+        </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>5.5</v>
+        <v>1.09</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>45867.625</v>
       </c>
     </row>
@@ -1053,20 +1039,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1079,13 +1065,13 @@
         <v>13</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
-        <v>19.5</v>
+        <v>2.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.2</v>
+        <v>10.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.2</v>
@@ -1100,58 +1086,55 @@
         <v>1.64</v>
       </c>
       <c r="V5" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['28', '35', '82']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y5" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AH5" t="n">
-        <v>3.55</v>
+        <v>4.85</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>45867.625</v>
       </c>
     </row>
@@ -1176,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1198,92 +1181,89 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.06</v>
+        <v>2.75</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>28</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>1.07</v>
+        <v>3.32</v>
       </c>
       <c r="P6" t="n">
-        <v>46</v>
+        <v>2.11</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.3</v>
+        <v>3.15</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>5.1</v>
+        <v>2.84</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>3.48</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>1.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.1</v>
+        <v>3.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.4</v>
+        <v>1.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.65</v>
+        <v>2.09</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['72', '76']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['80', '87']</t>
+        </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.35</v>
+        <v>1.46</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK6" s="3" t="n">
         <v>45867.66666666666</v>
       </c>
     </row>
@@ -1308,114 +1288,111 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M7" t="n">
+        <v>11</v>
+      </c>
+      <c r="N7" t="n">
+        <v>28</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z7" t="n">
         <v>3.4</v>
       </c>
-      <c r="N7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="P7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['8', '16', '37', '44', '75']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AH7" t="n">
-        <v>5.65</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AK7" s="3" t="n">
         <v>45867.66666666666</v>
       </c>
     </row>
@@ -1425,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,115 +1417,112 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['4', '44']</t>
+        </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
-        <v>45867.83333333334</v>
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>45867.77083333334</v>
       </c>
     </row>
     <row r="9">
@@ -1557,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,19 +1546,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1594,93 +1568,90 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>7.4</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>3.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.5</v>
+        <v>1.96</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.81</v>
+        <v>1.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>7.75</v>
+        <v>2.85</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
-        <v>45867.85416666666</v>
+        <v>1.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK9" s="3" t="n">
+        <v>45867.83333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1694,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,114 +1675,111 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N10" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X10" t="n">
         <v>3.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Y10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['12', '17']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.77</v>
       </c>
-      <c r="P10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="AI10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.25</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>10</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+      <c r="AK10" s="3" t="n">
         <v>45867.85416666666</v>
       </c>
     </row>
@@ -1821,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,115 +1804,112 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.75</v>
+        <v>3.81</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>8.5</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.62</v>
+        <v>6.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.48</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>2.37</v>
       </c>
       <c r="Y11" t="n">
-        <v>9</v>
+        <v>2.47</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AI11" t="n">
         <v>1.77</v>
       </c>
-      <c r="AG11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
-        <v>45867.875</v>
+      <c r="AJ11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AK11" s="3" t="n">
+        <v>45867.85416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1953,129 +1918,384 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['20', '27', '64', '82']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <v>45867.875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Valour FC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Cavalry FC</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['23', '56']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <v>45867.875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Goiás</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Remo</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI14" t="n">
         <v>1.57</v>
       </c>
-      <c r="P12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="AJ14" t="n">
         <v>3.1</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AK14" s="3" t="n">
         <v>45867.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-07-29.xlsx
+++ b/jogos_2025-07-29.xlsx
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Drita</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hamrun Spartans</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.39</v>
+        <v>13</v>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.83</v>
+        <v>10.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="T4" t="n">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>['28', '35', '82']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
       <c r="AG4" t="n">
-        <v>2.75</v>
+        <v>1.01</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.09</v>
+        <v>4.85</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45867.625</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Drita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.75</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.63</v>
       </c>
       <c r="U5" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['42']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.09</v>
       </c>
-      <c r="X5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['28', '35', '82']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>4.85</v>
-      </c>
       <c r="AI5" t="n">
-        <v>1.18</v>
+        <v>3.25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45867.625</v>
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.75</v>
+        <v>1.06</v>
       </c>
       <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>28</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z6" t="n">
         <v>3.4</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['8', '16', '37', '44', '75']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['72', '76']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['80', '87']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.46</v>
+        <v>10</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.96</v>
+        <v>7.3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45867.66666666666</v>
@@ -1288,109 +1288,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="M7" t="n">
-        <v>11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>28</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P7" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>7.1</v>
+        <v>3.48</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>3.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['8', '16', '37', '44', '75']</t>
+          <t>['72', '76']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['80', '87']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>1.46</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.07</v>
+        <v>2.02</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7.3</v>
+        <v>1.96</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45867.66666666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>3.81</v>
       </c>
       <c r="O10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.33</v>
+        <v>6.14</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.19</v>
+        <v>2.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['12', '17']</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.77</v>
       </c>
-      <c r="AI10" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45867.85416666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.81</v>
+        <v>3.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.14</v>
+        <v>4.33</v>
       </c>
       <c r="R11" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['12', '17']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.25</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['17']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.65</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45867.85416666666</v>
